--- a/data/trans_orig/P6902-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6902-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>20858</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39358</t>
+          <t>38935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>5165</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>16187</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28818</t>
+          <t>28901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>51351</t>
+          <t>50035</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71928</t>
+          <t>72351</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91323</t>
+          <t>90428</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21782</t>
+          <t>21381</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32462</t>
+          <t>32403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97503</t>
+          <t>98819</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120036</t>
+          <t>119953</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101022</t>
+          <t>102465</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134913</t>
+          <t>136272</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47749</t>
+          <t>47117</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69874</t>
+          <t>69993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>157397</t>
+          <t>157230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>197733</t>
+          <t>197565</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>152032</t>
+          <t>150673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185923</t>
+          <t>184480</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48697</t>
+          <t>48578</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70822</t>
+          <t>71454</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>207782</t>
+          <t>207950</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>248118</t>
+          <t>248285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,23%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48748</t>
+          <t>49476</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63735</t>
+          <t>63904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36371</t>
+          <t>36303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51046</t>
+          <t>51195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90475</t>
+          <t>90523</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111137</t>
+          <t>111842</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>81,01%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25327</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>12788</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27612</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26921</t>
+          <t>26216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47583</t>
+          <t>47535</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,43%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182842</t>
+          <t>185412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>226766</t>
+          <t>229307</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>99095</t>
+          <t>97668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>129325</t>
+          <t>126680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>292085</t>
+          <t>292908</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>343979</t>
+          <t>345489</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,9%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>245539</t>
+          <t>242998</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>289463</t>
+          <t>286893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90796</t>
+          <t>93441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121026</t>
+          <t>122453</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>348448</t>
+          <t>346938</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>400342</t>
+          <t>399519</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,7%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12518</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26249</t>
+          <t>26514</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13260</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25531</t>
+          <t>25315</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29524</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49477</t>
+          <t>49102</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30069</t>
+          <t>29804</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>43351</t>
+          <t>43800</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12404</t>
+          <t>12620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24675</t>
+          <t>24598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>44776</t>
+          <t>45151</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>64729</t>
+          <t>65409</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,4%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83903</t>
+          <t>84126</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115774</t>
+          <t>116061</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59287</t>
+          <t>59644</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82461</t>
+          <t>83416</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152931</t>
+          <t>152027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>191698</t>
+          <t>190613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,95%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>105965</t>
+          <t>105678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137836</t>
+          <t>137613</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49111</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>71928</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161613</t>
+          <t>162698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200380</t>
+          <t>201284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,97%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26074</t>
+          <t>25965</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38479</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>25598</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39347</t>
+          <t>39685</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57492</t>
+          <t>56603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>74556</t>
+          <t>75399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,59%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7610</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20015</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>20723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17854</t>
+          <t>17011</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34918</t>
+          <t>35807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,75%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>135610</t>
+          <t>134023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>169862</t>
+          <t>172898</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108010</t>
+          <t>107731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138217</t>
+          <t>138490</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>251774</t>
+          <t>250406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>299801</t>
+          <t>298969</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154284</t>
+          <t>151248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188536</t>
+          <t>190123</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77611</t>
+          <t>77338</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107818</t>
+          <t>108097</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>240173</t>
+          <t>241005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>288200</t>
+          <t>289568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,63%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15542</t>
+          <t>15770</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31554</t>
+          <t>31536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1888</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19745</t>
+          <t>21133</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36968</t>
+          <t>37014</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,29%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24027</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40039</t>
+          <t>39811</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16136</t>
+          <t>16071</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>36637</t>
+          <t>36591</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53860</t>
+          <t>52472</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69067</t>
+          <t>68392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97948</t>
+          <t>97828</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,7%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62481</t>
+          <t>62791</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83505</t>
+          <t>84944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137879</t>
+          <t>137554</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>176167</t>
+          <t>175758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,66%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>131434</t>
+          <t>131554</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160315</t>
+          <t>160990</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41060</t>
+          <t>39621</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>62084</t>
+          <t>61774</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>177780</t>
+          <t>178189</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>216068</t>
+          <t>216393</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,14%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35525</t>
+          <t>35033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50397</t>
+          <t>51085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44322</t>
+          <t>44089</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60734</t>
+          <t>60378</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84546</t>
+          <t>83389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106142</t>
+          <t>106833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,85%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13131</t>
+          <t>12443</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28003</t>
+          <t>28495</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>13330</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29386</t>
+          <t>29619</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31094</t>
+          <t>30403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52690</t>
+          <t>53847</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>39,24%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128939</t>
+          <t>131952</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>170316</t>
+          <t>170988</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115947</t>
+          <t>116377</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>145027</t>
+          <t>144767</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>255048</t>
+          <t>259253</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305583</t>
+          <t>307027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>54,36%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>178175</t>
+          <t>177503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219552</t>
+          <t>216539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>71271</t>
+          <t>71531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>100351</t>
+          <t>99921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>259205</t>
+          <t>257761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>309740</t>
+          <t>305535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,1%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que se siente nervioso y estresado en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9523</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20035</t>
+          <t>20438</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16451</t>
+          <t>16680</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17110</t>
+          <t>17329</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33901</t>
+          <t>33446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>61,71%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9179</t>
+          <t>8776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19691</t>
+          <t>20273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19959</t>
+          <t>19560</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>20754</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37090</t>
+          <t>36871</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>68,03%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115066</t>
+          <t>116453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149398</t>
+          <t>148812</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73607</t>
+          <t>78079</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>147688</t>
+          <t>148864</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196091</t>
+          <t>201767</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>286539</t>
+          <t>285854</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90182</t>
+          <t>90768</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124514</t>
+          <t>123127</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90680</t>
+          <t>89504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>164761</t>
+          <t>160289</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191409</t>
+          <t>192094</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>281857</t>
+          <t>276181</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>57,78%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52266</t>
+          <t>52793</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64924</t>
+          <t>65331</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73995</t>
+          <t>74195</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>83848</t>
+          <t>84037</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>131052</t>
+          <t>131230</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147118</t>
+          <t>147397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>92,0%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>16733</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6658</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>16500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>12824</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29169</t>
+          <t>28991</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>190246</t>
+          <t>190730</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>228055</t>
+          <t>227200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>159343</t>
+          <t>153253</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>242634</t>
+          <t>243025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>355661</t>
+          <t>350800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>456039</t>
+          <t>455802</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,83%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110265</t>
+          <t>111120</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>148074</t>
+          <t>147590</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111415</t>
+          <t>111024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>200796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>236330</t>
+          <t>236567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336708</t>
+          <t>341569</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,33%</t>
         </is>
       </c>
     </row>
